--- a/SG_Responsibility_Listing.xlsx
+++ b/SG_Responsibility_Listing.xlsx
@@ -1605,6 +1605,11 @@
           <t>HOA</t>
         </is>
       </c>
+      <c r="F52" s="39" t="inlineStr">
+        <is>
+          <t>Includes trimming trees away from roofs and gutters, and cleaning tree debris out of gutters (see the Building - Gutters row in each Condo section). Gutter repair/replacement stays with the Condo.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" t="n">
@@ -2159,7 +2164,17 @@
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Gutters &amp; leaders on the building: repair, re-pitch, re-attach, replace sections; full replacement within the roof replacement cycle; roof raking &amp; ice removal from gutters</t>
+        </is>
+      </c>
+      <c r="E88" s="39" t="inlineStr">
+        <is>
+          <t>Cleaning tree debris out of gutters (landscaping); trimming trees to keep branches off roofs and gutters; underground drain lines downspouts discharge into</t>
+        </is>
+      </c>
+      <c r="F88" s="39" t="inlineStr">
+        <is>
+          <t>[Clarified 2026-10] Split by the work done. Gutters &amp; leaders are part of the roof system (Condo bylaws: Condo maintains "roof and roof members"), so the Condo repairs and replaces them. What clogs them is the trees, and tree maintenance is the HOA's (Item 49; 1st Amend. §1(d)(i): the Condo land is an HOA Common Area), so cleaning tree debris is HOA landscaping. Moving cleaning to the HOA needs the HOA Board's agreement and a gutter-cleaning line in the HOA budget.</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2627,17 @@
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Gutters &amp; leaders on the building: repair, re-pitch, re-attach, replace sections; full replacement within the roof replacement cycle; roof raking &amp; ice removal from gutters</t>
+        </is>
+      </c>
+      <c r="E116" s="39" t="inlineStr">
+        <is>
+          <t>Cleaning tree debris out of gutters (landscaping); trimming trees to keep branches off roofs and gutters; underground drain lines downspouts discharge into</t>
+        </is>
+      </c>
+      <c r="F116" s="39" t="inlineStr">
+        <is>
+          <t>[Clarified 2026-10] Split by the work done. Gutters &amp; leaders are part of the roof system (Condo bylaws: Condo maintains "roof and roof members"), so the Condo repairs and replaces them. What clogs them is the trees, and tree maintenance is the HOA's (Item 49; 1st Amend. §1(d)(i): the Condo land is an HOA Common Area), so cleaning tree debris is HOA landscaping. Moving cleaning to the HOA needs the HOA Board's agreement and a gutter-cleaning line in the HOA budget.</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3061,17 @@
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Gutters &amp; leaders on the building: repair, re-pitch, re-attach, replace sections; full replacement within the roof replacement cycle; roof raking &amp; ice removal from gutters</t>
+        </is>
+      </c>
+      <c r="E144" s="39" t="inlineStr">
+        <is>
+          <t>Cleaning tree debris out of gutters (landscaping); trimming trees to keep branches off roofs and gutters; underground drain lines downspouts discharge into</t>
+        </is>
+      </c>
+      <c r="F144" s="39" t="inlineStr">
+        <is>
+          <t>[Clarified 2026-10] Split by the work done. Gutters &amp; leaders are part of the roof system (Condo bylaws: Condo maintains "roof and roof members"), so the Condo repairs and replaces them. What clogs them is the trees, and tree maintenance is the HOA's (Item 49; 1st Amend. §1(d)(i): the Condo land is an HOA Common Area), so cleaning tree debris is HOA landscaping. Moving cleaning to the HOA needs the HOA Board's agreement and a gutter-cleaning line in the HOA budget.</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3500,17 @@
       </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Gutters &amp; leaders on the building: repair, re-pitch, re-attach, replace sections; full replacement within the roof replacement cycle; roof raking &amp; ice removal from gutters</t>
+        </is>
+      </c>
+      <c r="E171" s="39" t="inlineStr">
+        <is>
+          <t>Cleaning tree debris out of gutters (landscaping); trimming trees to keep branches off roofs and gutters; underground drain lines downspouts discharge into</t>
+        </is>
+      </c>
+      <c r="F171" s="39" t="inlineStr">
+        <is>
+          <t>[Clarified 2026-10] Split by the work done. Gutters &amp; leaders are part of the roof system (Condo bylaws: Condo maintains "roof and roof members"), so the Condo repairs and replaces them. What clogs them is the trees, and tree maintenance is the HOA's (Item 49; 1st Amend. §1(d)(i): the Condo land is an HOA Common Area), so cleaning tree debris is HOA landscaping. Moving cleaning to the HOA needs the HOA Board's agreement and a gutter-cleaning line in the HOA budget.</t>
         </is>
       </c>
     </row>
